--- a/hmwebsite/helix/data/models.xlsx
+++ b/hmwebsite/helix/data/models.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\hmon.ir\hmwebsite\helix\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\git\hmon.ir\hmwebsite\helix\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29BADF34-F354-4EB1-9D47-0A885181001D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A3762B9-13F7-4C69-83CC-E2061C27BF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Models" sheetId="1" r:id="rId1"/>
@@ -4555,7 +4555,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -4626,10 +4626,9 @@
     <xf numFmtId="49" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -4639,21 +4638,20 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -4942,6 +4940,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:L526"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4960,16 +4959,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="71" t="s">
+      <c r="C1" s="69" t="s">
         <v>171</v>
       </c>
-      <c r="D1" s="71" t="s">
+      <c r="D1" s="69" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="30" t="s">
@@ -4997,7 +4996,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>1</v>
       </c>
@@ -5026,7 +5025,7 @@
       </c>
       <c r="K2" s="12"/>
     </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -5057,7 +5056,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>1</v>
       </c>
@@ -5088,7 +5087,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>1</v>
       </c>
@@ -5119,7 +5118,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>1</v>
       </c>
@@ -5150,7 +5149,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>1</v>
       </c>
@@ -5177,7 +5176,7 @@
       </c>
       <c r="K7" s="12"/>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>1</v>
       </c>
@@ -5208,7 +5207,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>1</v>
       </c>
@@ -5239,7 +5238,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>1</v>
       </c>
@@ -5270,7 +5269,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>1</v>
       </c>
@@ -5299,7 +5298,7 @@
       </c>
       <c r="K11" s="12"/>
     </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>1</v>
       </c>
@@ -5328,7 +5327,7 @@
       </c>
       <c r="K12" s="12"/>
     </row>
-    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>1</v>
       </c>
@@ -5359,7 +5358,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>1</v>
       </c>
@@ -5390,7 +5389,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>1</v>
       </c>
@@ -5421,7 +5420,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>1</v>
       </c>
@@ -5452,7 +5451,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>1</v>
       </c>
@@ -5483,7 +5482,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>1</v>
       </c>
@@ -5514,7 +5513,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <v>1</v>
       </c>
@@ -5545,7 +5544,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>1</v>
       </c>
@@ -5574,7 +5573,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <v>1</v>
       </c>
@@ -5603,7 +5602,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>1</v>
       </c>
@@ -5632,7 +5631,7 @@
       </c>
       <c r="K22" s="12"/>
     </row>
-    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <v>1</v>
       </c>
@@ -5663,7 +5662,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>1</v>
       </c>
@@ -5694,7 +5693,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>1</v>
       </c>
@@ -5725,7 +5724,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>1</v>
       </c>
@@ -5754,7 +5753,7 @@
       </c>
       <c r="K26" s="12"/>
     </row>
-    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>1</v>
       </c>
@@ -5783,7 +5782,7 @@
       </c>
       <c r="K27" s="12"/>
     </row>
-    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>1</v>
       </c>
@@ -5812,7 +5811,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
         <v>1</v>
       </c>
@@ -5841,7 +5840,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>1</v>
       </c>
@@ -5870,7 +5869,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
         <v>1</v>
       </c>
@@ -5897,7 +5896,7 @@
       </c>
       <c r="K31" s="12"/>
     </row>
-    <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <v>1</v>
       </c>
@@ -5926,7 +5925,7 @@
       </c>
       <c r="K32" s="12"/>
     </row>
-    <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
         <v>1</v>
       </c>
@@ -5955,7 +5954,7 @@
       </c>
       <c r="K33" s="12"/>
     </row>
-    <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <v>1</v>
       </c>
@@ -5986,7 +5985,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
         <v>1</v>
       </c>
@@ -6017,7 +6016,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
         <v>1</v>
       </c>
@@ -6048,7 +6047,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
         <v>1</v>
       </c>
@@ -6077,7 +6076,7 @@
       </c>
       <c r="K37" s="12"/>
     </row>
-    <row r="38" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
         <v>1</v>
       </c>
@@ -6106,7 +6105,7 @@
       </c>
       <c r="K38" s="12"/>
     </row>
-    <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
         <v>1</v>
       </c>
@@ -6135,7 +6134,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
         <v>1</v>
       </c>
@@ -6164,7 +6163,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
         <v>1</v>
       </c>
@@ -6195,7 +6194,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
         <v>1</v>
       </c>
@@ -6226,7 +6225,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
         <v>1</v>
       </c>
@@ -6257,7 +6256,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
         <v>1</v>
       </c>
@@ -6288,7 +6287,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
         <v>1</v>
       </c>
@@ -6315,7 +6314,7 @@
       </c>
       <c r="K45" s="12"/>
     </row>
-    <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
         <v>1</v>
       </c>
@@ -6344,7 +6343,7 @@
       </c>
       <c r="K46" s="12"/>
     </row>
-    <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
         <v>1</v>
       </c>
@@ -6373,7 +6372,7 @@
       </c>
       <c r="K47" s="12"/>
     </row>
-    <row r="48" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
         <v>1</v>
       </c>
@@ -6402,7 +6401,7 @@
       </c>
       <c r="K48" s="12"/>
     </row>
-    <row r="49" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
         <v>1</v>
       </c>
@@ -6435,7 +6434,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
         <v>1</v>
       </c>
@@ -6466,7 +6465,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
         <v>1</v>
       </c>
@@ -6497,7 +6496,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
         <v>1</v>
       </c>
@@ -6528,7 +6527,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
         <v>1</v>
       </c>
@@ -6559,7 +6558,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
         <v>1</v>
       </c>
@@ -6590,7 +6589,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
         <v>1</v>
       </c>
@@ -6621,7 +6620,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
         <v>1</v>
       </c>
@@ -6652,7 +6651,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
         <v>1</v>
       </c>
@@ -6685,7 +6684,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
         <v>1</v>
       </c>
@@ -6716,7 +6715,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="11">
         <v>1</v>
       </c>
@@ -6747,7 +6746,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="11">
         <v>1</v>
       </c>
@@ -6778,7 +6777,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="11">
         <v>1</v>
       </c>
@@ -6809,7 +6808,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="11">
         <v>1</v>
       </c>
@@ -6840,7 +6839,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="11">
         <v>1</v>
       </c>
@@ -6871,7 +6870,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="11">
         <v>1</v>
       </c>
@@ -6902,7 +6901,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="11">
         <v>1</v>
       </c>
@@ -6933,7 +6932,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="11">
         <v>1</v>
       </c>
@@ -6964,7 +6963,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="11">
         <v>1</v>
       </c>
@@ -6995,7 +6994,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="11">
         <v>1</v>
       </c>
@@ -7026,7 +7025,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="11">
         <v>1</v>
       </c>
@@ -7057,7 +7056,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="11">
         <v>1</v>
       </c>
@@ -7088,7 +7087,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="11">
         <v>1</v>
       </c>
@@ -7119,7 +7118,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="11">
         <v>1</v>
       </c>
@@ -7150,7 +7149,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="11">
         <v>1</v>
       </c>
@@ -7181,7 +7180,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="11">
         <v>1</v>
       </c>
@@ -7212,7 +7211,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="11">
         <v>1</v>
       </c>
@@ -7243,7 +7242,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="11">
         <v>1</v>
       </c>
@@ -7274,7 +7273,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="11">
         <v>1</v>
       </c>
@@ -7305,7 +7304,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="11">
         <v>1</v>
       </c>
@@ -7336,7 +7335,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="11">
         <v>1</v>
       </c>
@@ -7365,7 +7364,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="11">
         <v>1</v>
       </c>
@@ -7394,7 +7393,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="11">
         <v>1</v>
       </c>
@@ -7425,7 +7424,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="11">
         <v>1</v>
       </c>
@@ -7454,7 +7453,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="11">
         <v>1</v>
       </c>
@@ -7483,7 +7482,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="11">
         <v>1</v>
       </c>
@@ -7514,7 +7513,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="11">
         <v>1</v>
       </c>
@@ -7545,7 +7544,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="11">
         <v>1</v>
       </c>
@@ -7574,7 +7573,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="11">
         <v>1</v>
       </c>
@@ -7605,7 +7604,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="11">
         <v>1</v>
       </c>
@@ -7634,7 +7633,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="11">
         <v>1</v>
       </c>
@@ -7663,7 +7662,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="11">
         <v>1</v>
       </c>
@@ -7692,7 +7691,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="11">
         <v>1</v>
       </c>
@@ -7723,7 +7722,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="11">
         <v>1</v>
       </c>
@@ -7754,7 +7753,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="11">
         <v>1</v>
       </c>
@@ -7783,7 +7782,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="11">
         <v>1</v>
       </c>
@@ -7814,7 +7813,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="11">
         <v>1</v>
       </c>
@@ -7845,7 +7844,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="11">
         <v>1</v>
       </c>
@@ -7874,7 +7873,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="11">
         <v>1</v>
       </c>
@@ -7903,7 +7902,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="11">
         <v>1</v>
       </c>
@@ -7932,7 +7931,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="11">
         <v>1</v>
       </c>
@@ -7961,7 +7960,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="11">
         <v>1</v>
       </c>
@@ -7992,7 +7991,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="11">
         <v>1</v>
       </c>
@@ -8021,7 +8020,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="11">
         <v>1</v>
       </c>
@@ -8050,7 +8049,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="11">
         <v>1</v>
       </c>
@@ -8079,7 +8078,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="11">
         <v>1</v>
       </c>
@@ -8108,7 +8107,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="11">
         <v>1</v>
       </c>
@@ -8139,7 +8138,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="11">
         <v>1</v>
       </c>
@@ -8170,7 +8169,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="11">
         <v>1</v>
       </c>
@@ -8201,7 +8200,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="11">
         <v>1</v>
       </c>
@@ -8232,7 +8231,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="11">
         <v>1</v>
       </c>
@@ -8261,7 +8260,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="11">
         <v>1</v>
       </c>
@@ -8292,7 +8291,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="11">
         <v>1</v>
       </c>
@@ -8323,7 +8322,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="11">
         <v>1</v>
       </c>
@@ -8354,7 +8353,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="11">
         <v>1</v>
       </c>
@@ -8385,7 +8384,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="11">
         <v>1</v>
       </c>
@@ -8416,7 +8415,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="11">
         <v>1</v>
       </c>
@@ -8445,7 +8444,7 @@
       </c>
       <c r="K115" s="12"/>
     </row>
-    <row r="116" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="11">
         <v>1</v>
       </c>
@@ -8474,7 +8473,7 @@
       </c>
       <c r="K116" s="12"/>
     </row>
-    <row r="117" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="11">
         <v>1</v>
       </c>
@@ -8503,7 +8502,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="11">
         <v>1</v>
       </c>
@@ -8532,7 +8531,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="11">
         <v>1</v>
       </c>
@@ -8561,7 +8560,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="11">
         <v>1</v>
       </c>
@@ -8590,7 +8589,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="11">
         <v>1</v>
       </c>
@@ -8621,7 +8620,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="11">
         <v>1</v>
       </c>
@@ -8650,7 +8649,7 @@
       </c>
       <c r="K122" s="12"/>
     </row>
-    <row r="123" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="11">
         <v>1</v>
       </c>
@@ -8679,7 +8678,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="11">
         <v>1</v>
       </c>
@@ -8708,7 +8707,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="11">
         <v>1</v>
       </c>
@@ -8737,7 +8736,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="11">
         <v>1</v>
       </c>
@@ -8766,7 +8765,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="11">
         <v>1</v>
       </c>
@@ -8797,7 +8796,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="11">
         <v>1</v>
       </c>
@@ -8824,7 +8823,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="129" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="11">
         <v>1</v>
       </c>
@@ -8851,7 +8850,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="11">
         <v>1</v>
       </c>
@@ -8876,7 +8875,7 @@
       </c>
       <c r="K130" s="21"/>
     </row>
-    <row r="131" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="11">
         <v>1</v>
       </c>
@@ -8901,7 +8900,7 @@
       </c>
       <c r="K131" s="21"/>
     </row>
-    <row r="132" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="11">
         <v>1</v>
       </c>
@@ -8930,7 +8929,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="11">
         <v>1</v>
       </c>
@@ -8961,7 +8960,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="11">
         <v>1</v>
       </c>
@@ -8990,7 +8989,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="11">
         <v>1</v>
       </c>
@@ -9021,7 +9020,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="11">
         <v>1</v>
       </c>
@@ -9050,7 +9049,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="11">
         <v>1</v>
       </c>
@@ -9079,7 +9078,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="11">
         <v>1</v>
       </c>
@@ -9108,7 +9107,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="139" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="11">
         <v>1</v>
       </c>
@@ -9137,7 +9136,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="140" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="11">
         <v>1</v>
       </c>
@@ -9164,7 +9163,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="11">
         <v>1</v>
       </c>
@@ -9193,7 +9192,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="142" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="11">
         <v>1</v>
       </c>
@@ -9222,7 +9221,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="11">
         <v>1</v>
       </c>
@@ -9251,7 +9250,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="144" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="11">
         <v>1</v>
       </c>
@@ -9280,7 +9279,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="145" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="11">
         <v>1</v>
       </c>
@@ -9309,7 +9308,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="146" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="11">
         <v>1</v>
       </c>
@@ -9338,7 +9337,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="147" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="11">
         <v>1</v>
       </c>
@@ -9367,7 +9366,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="148" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="11">
         <v>1</v>
       </c>
@@ -9396,7 +9395,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="149" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="11">
         <v>1</v>
       </c>
@@ -9425,7 +9424,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="150" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="11">
         <v>1</v>
       </c>
@@ -9454,7 +9453,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="151" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="11">
         <v>1</v>
       </c>
@@ -9483,7 +9482,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="152" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="11">
         <v>1</v>
       </c>
@@ -9514,7 +9513,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="153" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="11">
         <v>1</v>
       </c>
@@ -9545,7 +9544,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="154" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="11">
         <v>1</v>
       </c>
@@ -9576,7 +9575,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="155" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="11">
         <v>1</v>
       </c>
@@ -9607,7 +9606,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="156" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="11">
         <v>1</v>
       </c>
@@ -9638,7 +9637,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="157" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="11">
         <v>1</v>
       </c>
@@ -9669,7 +9668,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="158" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="11">
         <v>1</v>
       </c>
@@ -9700,7 +9699,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="159" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="11">
         <v>1</v>
       </c>
@@ -9731,7 +9730,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="160" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="11">
         <v>1</v>
       </c>
@@ -9762,7 +9761,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="161" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="11">
         <v>1</v>
       </c>
@@ -9793,7 +9792,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="162" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="11">
         <v>1</v>
       </c>
@@ -9824,7 +9823,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="163" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="11">
         <v>1</v>
       </c>
@@ -9855,7 +9854,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="164" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="11">
         <v>1</v>
       </c>
@@ -9880,7 +9879,7 @@
       </c>
       <c r="K164" s="21"/>
     </row>
-    <row r="165" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="11">
         <v>1</v>
       </c>
@@ -9905,7 +9904,7 @@
       </c>
       <c r="K165" s="21"/>
     </row>
-    <row r="166" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="11">
         <v>1</v>
       </c>
@@ -9930,7 +9929,7 @@
       </c>
       <c r="K166" s="21"/>
     </row>
-    <row r="167" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="11">
         <v>1</v>
       </c>
@@ -9955,7 +9954,7 @@
       </c>
       <c r="K167" s="21"/>
     </row>
-    <row r="168" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="11">
         <v>1</v>
       </c>
@@ -9980,7 +9979,7 @@
       </c>
       <c r="K168" s="21"/>
     </row>
-    <row r="169" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="11">
         <v>1</v>
       </c>
@@ -10005,7 +10004,7 @@
       </c>
       <c r="K169" s="21"/>
     </row>
-    <row r="170" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="11">
         <v>1</v>
       </c>
@@ -10030,7 +10029,7 @@
       </c>
       <c r="K170" s="21"/>
     </row>
-    <row r="171" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="11">
         <v>1</v>
       </c>
@@ -10055,7 +10054,7 @@
       </c>
       <c r="K171" s="21"/>
     </row>
-    <row r="172" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="11">
         <v>1</v>
       </c>
@@ -10080,7 +10079,7 @@
       </c>
       <c r="K172" s="21"/>
     </row>
-    <row r="173" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="11">
         <v>1</v>
       </c>
@@ -10105,7 +10104,7 @@
       </c>
       <c r="K173" s="21"/>
     </row>
-    <row r="174" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="11">
         <v>1</v>
       </c>
@@ -10130,7 +10129,7 @@
       </c>
       <c r="K174" s="21"/>
     </row>
-    <row r="175" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="11">
         <v>1</v>
       </c>
@@ -10155,7 +10154,7 @@
       </c>
       <c r="K175" s="21"/>
     </row>
-    <row r="176" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="11">
         <v>1</v>
       </c>
@@ -10180,7 +10179,7 @@
       </c>
       <c r="K176" s="21"/>
     </row>
-    <row r="177" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="11">
         <v>1</v>
       </c>
@@ -10205,7 +10204,7 @@
       </c>
       <c r="K177" s="21"/>
     </row>
-    <row r="178" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="11">
         <v>1</v>
       </c>
@@ -10230,7 +10229,7 @@
       </c>
       <c r="K178" s="21"/>
     </row>
-    <row r="179" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="11">
         <v>1</v>
       </c>
@@ -10255,7 +10254,7 @@
       </c>
       <c r="K179" s="21"/>
     </row>
-    <row r="180" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="11">
         <v>1</v>
       </c>
@@ -10279,9 +10278,8 @@
         <v>921</v>
       </c>
       <c r="K180" s="21"/>
-      <c r="L180" s="69"/>
-    </row>
-    <row r="181" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="181" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="11">
         <v>1</v>
       </c>
@@ -10306,7 +10304,7 @@
       </c>
       <c r="K181" s="21"/>
     </row>
-    <row r="182" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="11">
         <v>1</v>
       </c>
@@ -10331,7 +10329,7 @@
       </c>
       <c r="K182" s="21"/>
     </row>
-    <row r="183" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="11">
         <v>1</v>
       </c>
@@ -10356,7 +10354,7 @@
       </c>
       <c r="K183" s="21"/>
     </row>
-    <row r="184" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="11">
         <v>1</v>
       </c>
@@ -10381,7 +10379,7 @@
       </c>
       <c r="K184" s="21"/>
     </row>
-    <row r="185" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="11">
         <v>1</v>
       </c>
@@ -10410,7 +10408,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="11">
         <v>1</v>
       </c>
@@ -10439,7 +10437,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="187" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="11">
         <v>1</v>
       </c>
@@ -10468,7 +10466,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="188" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="11">
         <v>1</v>
       </c>
@@ -10497,7 +10495,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="11">
         <v>1</v>
       </c>
@@ -10526,7 +10524,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="190" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="11">
         <v>1</v>
       </c>
@@ -10555,7 +10553,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="191" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="11">
         <v>1</v>
       </c>
@@ -10584,7 +10582,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="192" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="11">
         <v>1</v>
       </c>
@@ -10613,7 +10611,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="193" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="11">
         <v>1</v>
       </c>
@@ -10642,7 +10640,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="194" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="11">
         <v>1</v>
       </c>
@@ -10669,7 +10667,7 @@
       </c>
       <c r="K194" s="12"/>
     </row>
-    <row r="195" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="11">
         <v>1</v>
       </c>
@@ -10696,7 +10694,7 @@
       </c>
       <c r="K195" s="12"/>
     </row>
-    <row r="196" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="11">
         <v>1</v>
       </c>
@@ -10725,7 +10723,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="197" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="11">
         <v>1</v>
       </c>
@@ -10754,7 +10752,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="198" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="51">
         <v>1.04</v>
       </c>
@@ -10769,13 +10767,13 @@
       </c>
       <c r="E198" s="52"/>
       <c r="F198" s="52"/>
-      <c r="G198" s="53"/>
-      <c r="H198" s="53"/>
-      <c r="I198" s="53"/>
-      <c r="J198" s="53"/>
-      <c r="K198" s="54"/>
-    </row>
-    <row r="199" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G198" s="50"/>
+      <c r="H198" s="50"/>
+      <c r="I198" s="50"/>
+      <c r="J198" s="50"/>
+      <c r="K198" s="53"/>
+    </row>
+    <row r="199" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="51">
         <v>1.04</v>
       </c>
@@ -10790,13 +10788,13 @@
       </c>
       <c r="E199" s="52"/>
       <c r="F199" s="52"/>
-      <c r="G199" s="53"/>
-      <c r="H199" s="53"/>
-      <c r="I199" s="53"/>
-      <c r="J199" s="53"/>
-      <c r="K199" s="54"/>
-    </row>
-    <row r="200" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G199" s="50"/>
+      <c r="H199" s="50"/>
+      <c r="I199" s="50"/>
+      <c r="J199" s="50"/>
+      <c r="K199" s="53"/>
+    </row>
+    <row r="200" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="11">
         <v>1.06</v>
       </c>
@@ -10825,7 +10823,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="201" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="11">
         <v>1.06</v>
       </c>
@@ -10854,7 +10852,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="202" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="11">
         <v>1.06</v>
       </c>
@@ -10883,7 +10881,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="203" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="11">
         <v>1.06</v>
       </c>
@@ -10912,7 +10910,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="204" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="11">
         <v>1.06</v>
       </c>
@@ -10941,7 +10939,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="205" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="11">
         <v>1.06</v>
       </c>
@@ -10970,7 +10968,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="206" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="11">
         <v>1.06</v>
       </c>
@@ -10999,7 +10997,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="207" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="11">
         <v>1.06</v>
       </c>
@@ -11028,7 +11026,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="208" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="11">
         <v>1.06</v>
       </c>
@@ -11057,7 +11055,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="209" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="11">
         <v>1.06</v>
       </c>
@@ -11086,7 +11084,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="210" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="11">
         <v>1.06</v>
       </c>
@@ -11115,7 +11113,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="211" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="11">
         <v>1.06</v>
       </c>
@@ -11144,7 +11142,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="212" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="11">
         <v>1.06</v>
       </c>
@@ -11173,7 +11171,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="213" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="4">
         <v>2</v>
       </c>
@@ -11202,7 +11200,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="214" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="4">
         <v>2</v>
       </c>
@@ -11231,7 +11229,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="215" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="4">
         <v>2</v>
       </c>
@@ -11260,7 +11258,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="216" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="4">
         <v>2</v>
       </c>
@@ -11289,7 +11287,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="217" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="4">
         <v>2</v>
       </c>
@@ -11318,7 +11316,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="218" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="4">
         <v>2</v>
       </c>
@@ -11347,7 +11345,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="219" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="4">
         <v>2</v>
       </c>
@@ -11376,7 +11374,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="220" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="4">
         <v>2</v>
       </c>
@@ -11403,7 +11401,7 @@
       </c>
       <c r="K220" s="5"/>
     </row>
-    <row r="221" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="4">
         <v>2</v>
       </c>
@@ -11432,7 +11430,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="222" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="11">
         <v>2.1</v>
       </c>
@@ -11461,7 +11459,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="223" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="11">
         <v>2.1</v>
       </c>
@@ -11490,7 +11488,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="224" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="11">
         <v>2.1</v>
       </c>
@@ -11519,7 +11517,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="225" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="11">
         <v>2.1</v>
       </c>
@@ -11548,7 +11546,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="226" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="11">
         <v>2.1</v>
       </c>
@@ -11577,7 +11575,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="227" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="14">
         <v>2.2000000000000002</v>
       </c>
@@ -11606,7 +11604,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="228" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="14">
         <v>2.2000000000000002</v>
       </c>
@@ -11635,7 +11633,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="229" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="14">
         <v>2.2000000000000002</v>
       </c>
@@ -11664,7 +11662,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="230" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="14">
         <v>2.2000000000000002</v>
       </c>
@@ -11691,7 +11689,7 @@
       </c>
       <c r="K230" s="15"/>
     </row>
-    <row r="231" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="14">
         <v>2.2000000000000002</v>
       </c>
@@ -11718,7 +11716,7 @@
       </c>
       <c r="K231" s="15"/>
     </row>
-    <row r="232" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="14">
         <v>2.2000000000000002</v>
       </c>
@@ -11747,7 +11745,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="233" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="14">
         <v>2.2000000000000002</v>
       </c>
@@ -11776,7 +11774,7 @@
       </c>
       <c r="K233" s="15"/>
     </row>
-    <row r="234" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="14">
         <v>2.2000000000000002</v>
       </c>
@@ -11805,7 +11803,7 @@
       </c>
       <c r="K234" s="15"/>
     </row>
-    <row r="235" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="14">
         <v>2.2000000000000002</v>
       </c>
@@ -11834,7 +11832,7 @@
       </c>
       <c r="K235" s="15"/>
     </row>
-    <row r="236" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="14">
         <v>2.2000000000000002</v>
       </c>
@@ -11865,7 +11863,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="237" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="14">
         <v>2.2000000000000002</v>
       </c>
@@ -11896,7 +11894,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="238" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="14">
         <v>2.2000000000000002</v>
       </c>
@@ -11927,7 +11925,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="239" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="14">
         <v>2.2000000000000002</v>
       </c>
@@ -11958,7 +11956,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="240" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="14">
         <v>2.2000000000000002</v>
       </c>
@@ -11987,7 +11985,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="241" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="14">
         <v>2.2000000000000002</v>
       </c>
@@ -12016,7 +12014,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="242" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="14">
         <v>2.2000000000000002</v>
       </c>
@@ -12045,7 +12043,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="243" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="14">
         <v>2.2000000000000002</v>
       </c>
@@ -12074,7 +12072,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="244" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="14">
         <v>2.2000000000000002</v>
       </c>
@@ -12103,7 +12101,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="245" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="14">
         <v>2.2000000000000002</v>
       </c>
@@ -12132,7 +12130,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="246" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="14">
         <v>2.2000000000000002</v>
       </c>
@@ -12161,7 +12159,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="247" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="14">
         <v>2.2000000000000002</v>
       </c>
@@ -12190,7 +12188,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="248" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="14">
         <v>2.2000000000000002</v>
       </c>
@@ -12246,7 +12244,7 @@
       </c>
       <c r="K249" s="5"/>
     </row>
-    <row r="250" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="4">
         <v>2.2999999999999998</v>
       </c>
@@ -12277,7 +12275,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="251" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="4">
         <v>2.2999999999999998</v>
       </c>
@@ -12308,7 +12306,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="252" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="4">
         <v>2.2999999999999998</v>
       </c>
@@ -12339,7 +12337,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="253" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="4">
         <v>2.2999999999999998</v>
       </c>
@@ -12366,7 +12364,7 @@
       </c>
       <c r="K253" s="5"/>
     </row>
-    <row r="254" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="4">
         <v>2.2999999999999998</v>
       </c>
@@ -12393,7 +12391,7 @@
       </c>
       <c r="K254" s="5"/>
     </row>
-    <row r="255" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="4">
         <v>2.2999999999999998</v>
       </c>
@@ -12420,7 +12418,7 @@
       </c>
       <c r="K255" s="5"/>
     </row>
-    <row r="256" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="4">
         <v>2.2999999999999998</v>
       </c>
@@ -12449,7 +12447,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="257" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="4">
         <v>2.2999999999999998</v>
       </c>
@@ -12478,7 +12476,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="258" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="4">
         <v>2.2999999999999998</v>
       </c>
@@ -12507,7 +12505,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="259" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="4">
         <v>2.2999999999999998</v>
       </c>
@@ -12536,7 +12534,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="260" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="4">
         <v>2.2999999999999998</v>
       </c>
@@ -12565,7 +12563,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="261" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="4">
         <v>2.2999999999999998</v>
       </c>
@@ -12594,7 +12592,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="262" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="4">
         <v>2.2999999999999998</v>
       </c>
@@ -12623,7 +12621,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="263" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="11">
         <v>2.5</v>
       </c>
@@ -12652,7 +12650,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="264" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="11">
         <v>2.5</v>
       </c>
@@ -12681,7 +12679,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="265" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="11">
         <v>2.5</v>
       </c>
@@ -12712,7 +12710,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="266" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="11">
         <v>2.5</v>
       </c>
@@ -12743,7 +12741,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="267" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="11">
         <v>2.5</v>
       </c>
@@ -12774,7 +12772,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="268" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="11">
         <v>2.5</v>
       </c>
@@ -12805,7 +12803,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="269" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="11">
         <v>2.5</v>
       </c>
@@ -12836,7 +12834,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="270" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="11">
         <v>2.5</v>
       </c>
@@ -12867,7 +12865,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="271" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="11">
         <v>2.5</v>
       </c>
@@ -12898,7 +12896,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="272" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="11">
         <v>2.5</v>
       </c>
@@ -12929,7 +12927,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="273" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="11">
         <v>2.5</v>
       </c>
@@ -12960,7 +12958,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="274" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="11">
         <v>2.5</v>
       </c>
@@ -12991,7 +12989,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="275" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="11">
         <v>2.5</v>
       </c>
@@ -13022,7 +13020,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="276" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="11">
         <v>2.5</v>
       </c>
@@ -13053,7 +13051,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="277" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="11">
         <v>2.5</v>
       </c>
@@ -13084,7 +13082,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="278" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="11">
         <v>2.5</v>
       </c>
@@ -13115,7 +13113,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="279" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="11">
         <v>2.5</v>
       </c>
@@ -13146,7 +13144,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="280" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="11">
         <v>2.5</v>
       </c>
@@ -13175,7 +13173,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="281" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="11">
         <v>2.5</v>
       </c>
@@ -13208,7 +13206,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="282" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="11">
         <v>2.5</v>
       </c>
@@ -13239,7 +13237,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="283" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="11">
         <v>2.5</v>
       </c>
@@ -13270,7 +13268,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="284" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="11">
         <v>2.5</v>
       </c>
@@ -13301,7 +13299,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="285" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="11">
         <v>2.5</v>
       </c>
@@ -13332,7 +13330,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="286" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="11">
         <v>2.5</v>
       </c>
@@ -13363,7 +13361,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="287" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="11">
         <v>2.5</v>
       </c>
@@ -13394,7 +13392,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="288" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="11">
         <v>2.5</v>
       </c>
@@ -13425,7 +13423,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="289" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="11">
         <v>2.5</v>
       </c>
@@ -13456,7 +13454,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="290" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="11">
         <v>2.5</v>
       </c>
@@ -13487,7 +13485,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="291" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="11">
         <v>2.5</v>
       </c>
@@ -13518,7 +13516,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="292" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="11">
         <v>2.5</v>
       </c>
@@ -13549,7 +13547,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="293" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="11">
         <v>2.5</v>
       </c>
@@ -13580,7 +13578,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="294" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="11">
         <v>2.5</v>
       </c>
@@ -13611,7 +13609,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="295" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="11">
         <v>2.5</v>
       </c>
@@ -13642,7 +13640,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="296" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="11">
         <v>2.5</v>
       </c>
@@ -13673,7 +13671,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="297" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="11">
         <v>2.5</v>
       </c>
@@ -13704,7 +13702,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="298" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="11">
         <v>2.5</v>
       </c>
@@ -13735,7 +13733,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="299" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="11">
         <v>2.5</v>
       </c>
@@ -13766,7 +13764,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="300" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="11">
         <v>2.5</v>
       </c>
@@ -13797,7 +13795,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="301" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="11">
         <v>2.5</v>
       </c>
@@ -13828,7 +13826,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="302" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="11">
         <v>2.5</v>
       </c>
@@ -13859,7 +13857,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="303" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="11">
         <v>2.5</v>
       </c>
@@ -13890,7 +13888,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="304" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="11">
         <v>2.5</v>
       </c>
@@ -13919,7 +13917,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="305" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="11">
         <v>2.5</v>
       </c>
@@ -13950,7 +13948,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="306" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="11">
         <v>2.5</v>
       </c>
@@ -13981,7 +13979,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="307" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="11">
         <v>2.5</v>
       </c>
@@ -14012,7 +14010,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="308" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="11">
         <v>2.5</v>
       </c>
@@ -14043,7 +14041,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="309" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="11">
         <v>2.5</v>
       </c>
@@ -14074,7 +14072,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="310" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="11">
         <v>2.5</v>
       </c>
@@ -14103,7 +14101,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="311" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="11">
         <v>2.5</v>
       </c>
@@ -14132,7 +14130,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="312" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="11">
         <v>2.5</v>
       </c>
@@ -14161,7 +14159,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="11">
         <v>2.5</v>
       </c>
@@ -14192,7 +14190,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="314" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="11">
         <v>2.5</v>
       </c>
@@ -14223,7 +14221,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="315" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="11">
         <v>2.5</v>
       </c>
@@ -14254,7 +14252,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="316" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="11">
         <v>2.5</v>
       </c>
@@ -14285,7 +14283,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="317" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="11">
         <v>2.5</v>
       </c>
@@ -14316,7 +14314,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="318" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="11">
         <v>2.5</v>
       </c>
@@ -14347,7 +14345,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="319" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="11">
         <v>2.5</v>
       </c>
@@ -14376,7 +14374,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="320" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="11">
         <v>2.5</v>
       </c>
@@ -14407,7 +14405,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="321" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="11">
         <v>2.5</v>
       </c>
@@ -14438,7 +14436,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="322" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="11">
         <v>2.5</v>
       </c>
@@ -14469,7 +14467,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="323" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="11">
         <v>2.5</v>
       </c>
@@ -14500,7 +14498,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="324" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="11">
         <v>2.5</v>
       </c>
@@ -14529,7 +14527,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="325" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="11">
         <v>2.5</v>
       </c>
@@ -14560,7 +14558,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="326" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="11">
         <v>2.5</v>
       </c>
@@ -14591,7 +14589,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="327" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="11">
         <v>2.5</v>
       </c>
@@ -14620,7 +14618,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="328" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="11">
         <v>2.5</v>
       </c>
@@ -14651,7 +14649,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="329" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="11">
         <v>2.5</v>
       </c>
@@ -14682,7 +14680,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="330" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="11">
         <v>2.5</v>
       </c>
@@ -14713,7 +14711,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="331" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="11">
         <v>2.5</v>
       </c>
@@ -14742,7 +14740,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="332" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:11" ht="75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="11">
         <v>2.5</v>
       </c>
@@ -14771,7 +14769,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="333" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="11">
         <v>2.5</v>
       </c>
@@ -14800,7 +14798,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="334" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="11">
         <v>2.5</v>
       </c>
@@ -14831,7 +14829,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="335" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="11">
         <v>2.5</v>
       </c>
@@ -14860,7 +14858,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="336" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:11" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="11">
         <v>2.5</v>
       </c>
@@ -14891,7 +14889,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="337" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="11">
         <v>2.5</v>
       </c>
@@ -14922,7 +14920,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="338" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:11" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="11">
         <v>2.5</v>
       </c>
@@ -14953,7 +14951,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="11">
         <v>2.5</v>
       </c>
@@ -14984,7 +14982,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="11">
         <v>2.5</v>
       </c>
@@ -15015,7 +15013,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="11">
         <v>2.5</v>
       </c>
@@ -15046,7 +15044,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="11">
         <v>2.5</v>
       </c>
@@ -15077,7 +15075,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="11">
         <v>2.5</v>
       </c>
@@ -15104,7 +15102,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="11">
         <v>2.5</v>
       </c>
@@ -15131,7 +15129,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="11">
         <v>2.5</v>
       </c>
@@ -15158,7 +15156,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="11">
         <v>2.5</v>
       </c>
@@ -15185,7 +15183,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="11">
         <v>2.5</v>
       </c>
@@ -15212,7 +15210,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="348" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="11">
         <v>2.6</v>
       </c>
@@ -15241,7 +15239,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="349" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="11">
         <v>2.6</v>
       </c>
@@ -15270,7 +15268,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="350" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="11">
         <v>2.6</v>
       </c>
@@ -15299,7 +15297,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="351" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="11">
         <v>2.6</v>
       </c>
@@ -15328,7 +15326,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="11">
         <v>2.6</v>
       </c>
@@ -15357,7 +15355,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="11">
         <v>2.6</v>
       </c>
@@ -15384,7 +15382,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="4">
         <v>2.8</v>
       </c>
@@ -15413,7 +15411,7 @@
       </c>
       <c r="K354" s="6"/>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="4">
         <v>2.8</v>
       </c>
@@ -15442,7 +15440,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="4">
         <v>2.8</v>
       </c>
@@ -15471,7 +15469,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="4">
         <v>2.8</v>
       </c>
@@ -15500,7 +15498,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="4">
         <v>2.8</v>
       </c>
@@ -15529,7 +15527,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="4">
         <v>2.8</v>
       </c>
@@ -15558,7 +15556,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="4">
         <v>2.8</v>
       </c>
@@ -15587,7 +15585,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="4">
         <v>2.8</v>
       </c>
@@ -15618,7 +15616,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="4">
         <v>2.8</v>
       </c>
@@ -15649,7 +15647,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="4">
         <v>2.8</v>
       </c>
@@ -15680,7 +15678,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="4">
         <v>2.8</v>
       </c>
@@ -15711,7 +15709,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="4">
         <v>2.8</v>
       </c>
@@ -15742,7 +15740,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="4">
         <v>2.8</v>
       </c>
@@ -15773,7 +15771,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="4">
         <v>2.8</v>
       </c>
@@ -15802,7 +15800,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="368" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:11" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="4">
         <v>2.8</v>
       </c>
@@ -15831,7 +15829,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="369" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:11" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="4">
         <v>2.8</v>
       </c>
@@ -15858,7 +15856,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2">
         <v>2.9</v>
       </c>
@@ -15889,7 +15887,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2">
         <v>2.9</v>
       </c>
@@ -15920,8 +15918,8 @@
         <v>947</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A372" s="61">
+    <row r="372" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A372" s="60">
         <v>2.9</v>
       </c>
       <c r="B372" s="19" t="s">
@@ -15933,25 +15931,25 @@
       <c r="D372" s="19" t="s">
         <v>1257</v>
       </c>
-      <c r="E372" s="62" t="s">
+      <c r="E372" s="61" t="s">
         <v>1199</v>
       </c>
-      <c r="F372" s="62"/>
-      <c r="G372" s="64"/>
+      <c r="F372" s="61"/>
+      <c r="G372" s="63"/>
       <c r="H372" s="20" t="s">
         <v>627</v>
       </c>
-      <c r="I372" s="66" t="s">
+      <c r="I372" s="65" t="s">
         <v>894</v>
       </c>
       <c r="J372" s="19" t="s">
         <v>903</v>
       </c>
-      <c r="K372" s="67" t="s">
+      <c r="K372" s="66" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2">
         <v>2.9</v>
       </c>
@@ -15980,7 +15978,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2">
         <v>2.9</v>
       </c>
@@ -16009,7 +16007,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2">
         <v>2.9</v>
       </c>
@@ -16040,7 +16038,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2">
         <v>2.9</v>
       </c>
@@ -16071,7 +16069,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2">
         <v>2.9</v>
       </c>
@@ -16098,7 +16096,7 @@
       </c>
       <c r="K377" s="7"/>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2">
         <v>2.9</v>
       </c>
@@ -16125,7 +16123,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="16">
         <v>3</v>
       </c>
@@ -16156,7 +16154,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="16">
         <v>3</v>
       </c>
@@ -16187,7 +16185,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="16">
         <v>3</v>
       </c>
@@ -16218,7 +16216,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="16">
         <v>3</v>
       </c>
@@ -16251,7 +16249,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="16">
         <v>3</v>
       </c>
@@ -16282,7 +16280,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="384" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:11" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="16">
         <v>3</v>
       </c>
@@ -16309,7 +16307,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="385" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="16">
         <v>3</v>
       </c>
@@ -16336,7 +16334,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="386" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="16">
         <v>3</v>
       </c>
@@ -16363,7 +16361,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="387" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="16">
         <v>3</v>
       </c>
@@ -16392,7 +16390,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="388" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="16">
         <v>3</v>
       </c>
@@ -16423,7 +16421,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="389" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="16">
         <v>3</v>
       </c>
@@ -16450,7 +16448,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="390" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="16">
         <v>3</v>
       </c>
@@ -16479,7 +16477,7 @@
       </c>
       <c r="K390" s="18"/>
     </row>
-    <row r="391" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="16">
         <v>3</v>
       </c>
@@ -16508,7 +16506,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="392" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="16">
         <v>3</v>
       </c>
@@ -16539,7 +16537,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="393" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:12" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="16">
         <v>3</v>
       </c>
@@ -16566,7 +16564,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="394" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="16">
         <v>3</v>
       </c>
@@ -16593,7 +16591,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="395" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="16">
         <v>3</v>
       </c>
@@ -16620,7 +16618,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="396" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="16">
         <v>3</v>
       </c>
@@ -16647,7 +16645,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="397" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="16">
         <v>3</v>
       </c>
@@ -16676,7 +16674,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="398" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="16">
         <v>3</v>
       </c>
@@ -16705,7 +16703,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="399" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="16">
         <v>3</v>
       </c>
@@ -16732,7 +16730,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="400" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="11">
         <v>3.1</v>
       </c>
@@ -16764,7 +16762,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="401" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:12" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="11">
         <v>3.1</v>
       </c>
@@ -16794,7 +16792,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="402" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:12" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="11">
         <v>3.1</v>
       </c>
@@ -16823,7 +16821,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="403" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="11">
         <v>3.1</v>
       </c>
@@ -16851,7 +16849,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="404" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="11">
         <v>3.1</v>
       </c>
@@ -16878,7 +16876,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="405" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="11">
         <v>3.1</v>
       </c>
@@ -16905,7 +16903,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="406" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="4">
         <v>3.15</v>
       </c>
@@ -16932,7 +16930,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="407" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="4">
         <v>3.15</v>
       </c>
@@ -16961,7 +16959,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="408" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="4">
         <v>3.15</v>
       </c>
@@ -16990,7 +16988,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="409" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="4">
         <v>3.15</v>
       </c>
@@ -17017,7 +17015,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="410" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="4">
         <v>3.15</v>
       </c>
@@ -17044,7 +17042,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="411" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="4">
         <v>3.15</v>
       </c>
@@ -17071,7 +17069,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="412" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:12" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="4">
         <v>3.15</v>
       </c>
@@ -17098,7 +17096,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="413" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:12" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="4">
         <v>3.15</v>
       </c>
@@ -17125,7 +17123,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="414" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="4">
         <v>3.15</v>
       </c>
@@ -17156,7 +17154,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="415" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="4">
         <v>3.15</v>
       </c>
@@ -17187,7 +17185,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="416" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="4">
         <v>3.15</v>
       </c>
@@ -17216,7 +17214,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="417" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:11" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="4">
         <v>3.15</v>
       </c>
@@ -17245,7 +17243,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="418" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:11" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="4">
         <v>3.15</v>
       </c>
@@ -17274,7 +17272,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="419" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:11" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="4">
         <v>3.15</v>
       </c>
@@ -17303,7 +17301,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="420" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:11" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" s="4">
         <v>3.15</v>
       </c>
@@ -17332,7 +17330,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" s="4">
         <v>3.15</v>
       </c>
@@ -17361,7 +17359,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="422" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:11" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" s="4">
         <v>3.15</v>
       </c>
@@ -17390,7 +17388,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="423" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:11" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" s="4">
         <v>3.15</v>
       </c>
@@ -17419,7 +17417,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="424" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:11" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" s="4">
         <v>3.15</v>
       </c>
@@ -17448,7 +17446,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="425" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:11" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" s="4">
         <v>3.15</v>
       </c>
@@ -17477,7 +17475,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="426" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:11" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" s="4">
         <v>3.15</v>
       </c>
@@ -17506,7 +17504,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="427" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:11" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" s="4">
         <v>3.15</v>
       </c>
@@ -17535,7 +17533,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="428" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:11" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" s="4">
         <v>3.15</v>
       </c>
@@ -17564,7 +17562,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="429" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:11" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" s="4">
         <v>3.15</v>
       </c>
@@ -17593,7 +17591,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="430" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:11" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" s="4">
         <v>3.15</v>
       </c>
@@ -17622,7 +17620,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="431" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:11" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" s="4">
         <v>3.15</v>
       </c>
@@ -17651,7 +17649,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="4">
         <v>3.15</v>
       </c>
@@ -17678,7 +17676,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" s="4">
         <v>3.15</v>
       </c>
@@ -17705,7 +17703,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="434" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:11" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="4">
         <v>3.15</v>
       </c>
@@ -17732,7 +17730,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="43">
         <v>3.5</v>
       </c>
@@ -17761,7 +17759,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" s="43">
         <v>3.5</v>
       </c>
@@ -17790,7 +17788,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="437" spans="1:11" ht="240" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:11" ht="240" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="43">
         <v>3.5</v>
       </c>
@@ -17819,7 +17817,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="438" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:11" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" s="43">
         <v>3.5</v>
       </c>
@@ -17848,7 +17846,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" s="43">
         <v>3.5</v>
       </c>
@@ -17877,7 +17875,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" s="43">
         <v>3.5</v>
       </c>
@@ -17906,7 +17904,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="43">
         <v>3.5</v>
       </c>
@@ -17935,7 +17933,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" s="43">
         <v>3.5</v>
       </c>
@@ -17964,7 +17962,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="43">
         <v>3.5</v>
       </c>
@@ -17993,7 +17991,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="444" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="43">
         <v>3.5</v>
       </c>
@@ -18022,7 +18020,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="445" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" s="43">
         <v>3.5</v>
       </c>
@@ -18053,7 +18051,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" s="43">
         <v>3.5</v>
       </c>
@@ -18084,7 +18082,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="447" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" s="43">
         <v>3.5</v>
       </c>
@@ -18115,7 +18113,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="448" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" s="43">
         <v>3.5</v>
       </c>
@@ -18146,7 +18144,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="449" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" s="43">
         <v>3.5</v>
       </c>
@@ -18177,7 +18175,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="450" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" s="43">
         <v>3.5</v>
       </c>
@@ -18208,7 +18206,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="451" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" s="43">
         <v>3.5</v>
       </c>
@@ -18239,7 +18237,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="452" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" s="43">
         <v>3.5</v>
       </c>
@@ -18270,7 +18268,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="453" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" s="43">
         <v>3.5</v>
       </c>
@@ -18301,7 +18299,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="454" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" s="43">
         <v>3.5</v>
       </c>
@@ -18332,7 +18330,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" s="43">
         <v>3.5</v>
       </c>
@@ -18363,7 +18361,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" s="43">
         <v>3.5</v>
       </c>
@@ -18394,7 +18392,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" s="43">
         <v>3.5</v>
       </c>
@@ -18425,7 +18423,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" s="43">
         <v>3.5</v>
       </c>
@@ -18456,7 +18454,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="459" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" s="43">
         <v>3.5</v>
       </c>
@@ -18487,7 +18485,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="460" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" s="43">
         <v>3.5</v>
       </c>
@@ -18518,7 +18516,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="461" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" s="43">
         <v>3.5</v>
       </c>
@@ -18549,7 +18547,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="462" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" s="43">
         <v>3.5</v>
       </c>
@@ -18580,7 +18578,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="463" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" s="43">
         <v>3.5</v>
       </c>
@@ -18611,7 +18609,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="464" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" s="43">
         <v>3.5</v>
       </c>
@@ -18642,7 +18640,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" s="43">
         <v>3.5</v>
       </c>
@@ -18673,7 +18671,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="466" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" s="43">
         <v>3.5</v>
       </c>
@@ -18704,7 +18702,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="467" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" s="43">
         <v>3.5</v>
       </c>
@@ -18735,7 +18733,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="468" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" s="43">
         <v>3.5</v>
       </c>
@@ -18766,7 +18764,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="469" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" s="43">
         <v>3.5</v>
       </c>
@@ -18795,7 +18793,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="470" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" s="43">
         <v>3.5</v>
       </c>
@@ -18824,7 +18822,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="471" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" s="43">
         <v>3.5</v>
       </c>
@@ -18840,7 +18838,7 @@
       <c r="E471" s="44"/>
       <c r="F471" s="44"/>
       <c r="G471" s="44"/>
-      <c r="H471" s="65" t="s">
+      <c r="H471" s="64" t="s">
         <v>1188</v>
       </c>
       <c r="I471" s="44" t="s">
@@ -18849,11 +18847,11 @@
       <c r="J471" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="K471" s="68" t="s">
+      <c r="K471" s="67" t="s">
         <v>1246</v>
       </c>
     </row>
-    <row r="472" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" s="43">
         <v>3.5</v>
       </c>
@@ -18880,7 +18878,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="473" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" s="43">
         <v>3.5</v>
       </c>
@@ -18907,7 +18905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="474" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" s="43">
         <v>3.5</v>
       </c>
@@ -18936,7 +18934,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="475" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:11" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" s="43">
         <v>3.5</v>
       </c>
@@ -18971,7 +18969,7 @@
         <v>3</v>
       </c>
       <c r="C476" s="38" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D476" s="38" t="s">
         <v>1262</v>
@@ -18986,13 +18984,13 @@
         <v>1277</v>
       </c>
       <c r="J476" s="38" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="K476" s="40" t="s">
         <v>1273</v>
       </c>
     </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" s="37">
         <v>3.6</v>
       </c>
@@ -19021,7 +19019,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" s="37">
         <v>3.6</v>
       </c>
@@ -19048,7 +19046,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="479" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" s="37">
         <v>3.6</v>
       </c>
@@ -19077,7 +19075,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="480" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" s="37">
         <v>3.6</v>
       </c>
@@ -19106,7 +19104,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="481" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" s="37">
         <v>3.6</v>
       </c>
@@ -19135,7 +19133,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="482" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" s="37">
         <v>3.6</v>
       </c>
@@ -19162,7 +19160,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="483" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" s="37">
         <v>3.6</v>
       </c>
@@ -19191,7 +19189,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="484" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" s="49">
         <v>3.6</v>
       </c>
@@ -19220,7 +19218,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="485" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" s="37">
         <v>3.6</v>
       </c>
@@ -19251,7 +19249,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="486" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" s="37">
         <v>3.6</v>
       </c>
@@ -19282,7 +19280,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="487" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" s="37">
         <v>3.6</v>
       </c>
@@ -19313,7 +19311,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="488" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" s="37">
         <v>3.6</v>
       </c>
@@ -19342,7 +19340,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="489" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" s="37">
         <v>3.6</v>
       </c>
@@ -19371,7 +19369,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="490" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" s="37">
         <v>3.6</v>
       </c>
@@ -19400,7 +19398,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="491" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" s="37">
         <v>3.6</v>
       </c>
@@ -19428,9 +19426,9 @@
       <c r="K491" s="40" t="s">
         <v>1269</v>
       </c>
-      <c r="L491" s="60"/>
-    </row>
-    <row r="492" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L491" s="59"/>
+    </row>
+    <row r="492" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" s="4">
         <v>3.7</v>
       </c>
@@ -19459,7 +19457,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="493" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" s="4">
         <v>3.7</v>
       </c>
@@ -19488,7 +19486,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="494" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" s="4">
         <v>3.7</v>
       </c>
@@ -19517,7 +19515,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="495" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" s="4">
         <v>3.7</v>
       </c>
@@ -19544,7 +19542,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="496" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" s="4">
         <v>3.7</v>
       </c>
@@ -19571,7 +19569,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="497" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" s="4">
         <v>3.7</v>
       </c>
@@ -19585,7 +19583,7 @@
         <v>1311</v>
       </c>
       <c r="E497" s="35"/>
-      <c r="F497" s="63"/>
+      <c r="F497" s="62"/>
       <c r="G497" s="5"/>
       <c r="H497" s="5" t="s">
         <v>565</v>
@@ -19598,7 +19596,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="498" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" s="4">
         <v>3.7</v>
       </c>
@@ -19625,7 +19623,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="499" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" s="4">
         <v>3.7</v>
       </c>
@@ -19651,11 +19649,11 @@
       <c r="K499" s="6" t="s">
         <v>1330</v>
       </c>
-      <c r="L499" s="59" t="s">
+      <c r="L499" s="58" t="s">
         <v>1412</v>
       </c>
     </row>
-    <row r="500" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" s="4">
         <v>3.7</v>
       </c>
@@ -19669,7 +19667,7 @@
         <v>1316</v>
       </c>
       <c r="E500" s="35"/>
-      <c r="F500" s="63"/>
+      <c r="F500" s="62"/>
       <c r="G500" s="5"/>
       <c r="H500" s="5" t="s">
         <v>565</v>
@@ -19682,7 +19680,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="501" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" s="4">
         <v>3.7</v>
       </c>
@@ -19711,7 +19709,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="502" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" s="4">
         <v>3.7</v>
       </c>
@@ -19742,7 +19740,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="503" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" s="4">
         <v>3.7</v>
       </c>
@@ -19773,7 +19771,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="504" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" s="4">
         <v>3.7</v>
       </c>
@@ -19787,7 +19785,7 @@
         <v>1339</v>
       </c>
       <c r="E504" s="35"/>
-      <c r="F504" s="59" t="s">
+      <c r="F504" s="58" t="s">
         <v>1399</v>
       </c>
       <c r="G504" s="5"/>
@@ -19804,7 +19802,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="505" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" s="4">
         <v>3.7</v>
       </c>
@@ -19835,7 +19833,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="506" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" s="4">
         <v>3.7</v>
       </c>
@@ -19864,7 +19862,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="507" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" s="4">
         <v>3.7</v>
       </c>
@@ -19893,7 +19891,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="508" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" s="4">
         <v>3.7</v>
       </c>
@@ -19924,7 +19922,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="509" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" s="4">
         <v>3.7</v>
       </c>
@@ -19955,7 +19953,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="510" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" s="4">
         <v>3.7</v>
       </c>
@@ -19986,7 +19984,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="511" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" s="4">
         <v>3.7</v>
       </c>
@@ -20015,7 +20013,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="512" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" s="4">
         <v>3.7</v>
       </c>
@@ -20044,7 +20042,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="513" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" s="4">
         <v>3.7</v>
       </c>
@@ -20069,7 +20067,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="514" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" s="4">
         <v>3.7</v>
       </c>
@@ -20096,7 +20094,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="515" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:11" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" s="4">
         <v>3.7</v>
       </c>
@@ -20123,325 +20121,332 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="516" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A516" s="55">
+    <row r="516" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A516" s="54">
         <v>3.8</v>
       </c>
-      <c r="B516" s="56" t="s">
+      <c r="B516" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="C516" s="56" t="s">
+      <c r="C516" s="55" t="s">
         <v>539</v>
       </c>
-      <c r="D516" s="56" t="s">
+      <c r="D516" s="55" t="s">
         <v>1419</v>
       </c>
-      <c r="E516" s="57"/>
-      <c r="F516" s="57"/>
-      <c r="G516" s="56"/>
-      <c r="H516" s="56" t="s">
+      <c r="E516" s="56"/>
+      <c r="F516" s="56"/>
+      <c r="G516" s="55"/>
+      <c r="H516" s="55" t="s">
         <v>1421</v>
       </c>
-      <c r="I516" s="56" t="s">
+      <c r="I516" s="55" t="s">
         <v>1446</v>
       </c>
-      <c r="J516" s="56" t="s">
+      <c r="J516" s="55" t="s">
         <v>905</v>
       </c>
-      <c r="K516" s="58" t="s">
+      <c r="K516" s="57" t="s">
         <v>1442</v>
       </c>
     </row>
-    <row r="517" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A517" s="55">
+    <row r="517" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A517" s="54">
         <v>3.8</v>
       </c>
-      <c r="B517" s="56" t="s">
+      <c r="B517" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="C517" s="56" t="s">
+      <c r="C517" s="55" t="s">
         <v>539</v>
       </c>
-      <c r="D517" s="56" t="s">
+      <c r="D517" s="55" t="s">
         <v>1420</v>
       </c>
-      <c r="E517" s="57"/>
-      <c r="F517" s="57"/>
-      <c r="G517" s="56"/>
-      <c r="H517" s="56" t="s">
+      <c r="E517" s="56"/>
+      <c r="F517" s="56"/>
+      <c r="G517" s="55"/>
+      <c r="H517" s="55" t="s">
         <v>1421</v>
       </c>
-      <c r="I517" s="56" t="s">
+      <c r="I517" s="55" t="s">
         <v>1447</v>
       </c>
-      <c r="J517" s="56" t="s">
+      <c r="J517" s="55" t="s">
         <v>905</v>
       </c>
-      <c r="K517" s="58" t="s">
+      <c r="K517" s="57" t="s">
         <v>1443</v>
       </c>
     </row>
-    <row r="518" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A518" s="55">
+    <row r="518" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A518" s="54">
         <v>3.8</v>
       </c>
-      <c r="B518" s="56" t="s">
+      <c r="B518" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="C518" s="56" t="s">
+      <c r="C518" s="55" t="s">
         <v>539</v>
       </c>
-      <c r="D518" s="56" t="s">
+      <c r="D518" s="55" t="s">
         <v>1418</v>
       </c>
-      <c r="E518" s="57"/>
-      <c r="F518" s="57"/>
-      <c r="G518" s="56"/>
-      <c r="H518" s="56" t="s">
+      <c r="E518" s="56"/>
+      <c r="F518" s="56"/>
+      <c r="G518" s="55"/>
+      <c r="H518" s="55" t="s">
         <v>845</v>
       </c>
-      <c r="I518" s="56" t="s">
+      <c r="I518" s="55" t="s">
         <v>1448</v>
       </c>
-      <c r="J518" s="56" t="s">
+      <c r="J518" s="55" t="s">
         <v>905</v>
       </c>
-      <c r="K518" s="58" t="s">
+      <c r="K518" s="57" t="s">
         <v>1444</v>
       </c>
     </row>
-    <row r="519" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A519" s="55">
+    <row r="519" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A519" s="54">
         <v>3.8</v>
       </c>
-      <c r="B519" s="56" t="s">
+      <c r="B519" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="C519" s="56" t="s">
+      <c r="C519" s="55" t="s">
         <v>539</v>
       </c>
-      <c r="D519" s="56" t="s">
+      <c r="D519" s="55" t="s">
         <v>1417</v>
       </c>
-      <c r="E519" s="57"/>
-      <c r="F519" s="57"/>
-      <c r="G519" s="56"/>
-      <c r="H519" s="56" t="s">
+      <c r="E519" s="56"/>
+      <c r="F519" s="56"/>
+      <c r="G519" s="55"/>
+      <c r="H519" s="55" t="s">
         <v>845</v>
       </c>
-      <c r="I519" s="56" t="s">
+      <c r="I519" s="55" t="s">
         <v>1449</v>
       </c>
-      <c r="J519" s="56" t="s">
+      <c r="J519" s="55" t="s">
         <v>905</v>
       </c>
-      <c r="K519" s="58" t="s">
+      <c r="K519" s="57" t="s">
         <v>1445</v>
       </c>
     </row>
-    <row r="520" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A520" s="55">
+    <row r="520" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A520" s="54">
         <v>3.8</v>
       </c>
-      <c r="B520" s="56" t="s">
+      <c r="B520" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="C520" s="56" t="s">
+      <c r="C520" s="55" t="s">
         <v>539</v>
       </c>
-      <c r="D520" s="56" t="s">
+      <c r="D520" s="55" t="s">
         <v>1422</v>
       </c>
-      <c r="E520" s="57"/>
-      <c r="F520" s="57"/>
-      <c r="G520" s="56"/>
-      <c r="H520" s="56" t="s">
+      <c r="E520" s="56"/>
+      <c r="F520" s="56"/>
+      <c r="G520" s="55"/>
+      <c r="H520" s="55" t="s">
         <v>568</v>
       </c>
-      <c r="I520" s="56" t="s">
+      <c r="I520" s="55" t="s">
         <v>1426</v>
       </c>
-      <c r="J520" s="56" t="s">
+      <c r="J520" s="55" t="s">
         <v>905</v>
       </c>
-      <c r="K520" s="58" t="s">
+      <c r="K520" s="57" t="s">
         <v>1425</v>
       </c>
     </row>
-    <row r="521" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A521" s="55">
+    <row r="521" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A521" s="54">
         <v>3.8</v>
       </c>
-      <c r="B521" s="56" t="s">
+      <c r="B521" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="C521" s="56" t="s">
+      <c r="C521" s="55" t="s">
         <v>539</v>
       </c>
-      <c r="D521" s="56" t="s">
+      <c r="D521" s="55" t="s">
         <v>1423</v>
       </c>
-      <c r="E521" s="57"/>
-      <c r="F521" s="57"/>
-      <c r="G521" s="56"/>
-      <c r="H521" s="56" t="s">
+      <c r="E521" s="56"/>
+      <c r="F521" s="56"/>
+      <c r="G521" s="55"/>
+      <c r="H521" s="55" t="s">
         <v>568</v>
       </c>
-      <c r="I521" s="56" t="s">
+      <c r="I521" s="55" t="s">
         <v>1427</v>
       </c>
-      <c r="J521" s="56" t="s">
+      <c r="J521" s="55" t="s">
         <v>905</v>
       </c>
-      <c r="K521" s="58" t="s">
+      <c r="K521" s="57" t="s">
         <v>1424</v>
       </c>
     </row>
-    <row r="522" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A522" s="55">
+    <row r="522" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A522" s="54">
         <v>3.8</v>
       </c>
-      <c r="B522" s="56" t="s">
+      <c r="B522" s="55" t="s">
         <v>170</v>
       </c>
-      <c r="C522" s="56" t="s">
+      <c r="C522" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="D522" s="56" t="s">
+      <c r="D522" s="55" t="s">
         <v>1428</v>
       </c>
-      <c r="E522" s="57"/>
-      <c r="F522" s="57"/>
-      <c r="G522" s="56"/>
-      <c r="H522" s="56" t="s">
+      <c r="E522" s="56"/>
+      <c r="F522" s="56"/>
+      <c r="G522" s="55"/>
+      <c r="H522" s="55" t="s">
         <v>568</v>
       </c>
-      <c r="I522" s="56" t="s">
+      <c r="I522" s="55" t="s">
         <v>1440</v>
       </c>
-      <c r="J522" s="56" t="s">
+      <c r="J522" s="55" t="s">
         <v>903</v>
       </c>
-      <c r="K522" s="58" t="s">
+      <c r="K522" s="57" t="s">
         <v>1431</v>
       </c>
     </row>
-    <row r="523" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A523" s="55">
+    <row r="523" spans="1:11" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A523" s="54">
         <v>3.8</v>
       </c>
-      <c r="B523" s="56" t="s">
+      <c r="B523" s="55" t="s">
         <v>170</v>
       </c>
-      <c r="C523" s="56" t="s">
+      <c r="C523" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="D523" s="56" t="s">
+      <c r="D523" s="55" t="s">
         <v>1430</v>
       </c>
-      <c r="E523" s="57"/>
-      <c r="F523" s="57"/>
-      <c r="G523" s="56"/>
-      <c r="H523" s="56" t="s">
+      <c r="E523" s="56"/>
+      <c r="F523" s="56"/>
+      <c r="G523" s="55"/>
+      <c r="H523" s="55" t="s">
         <v>641</v>
       </c>
-      <c r="I523" s="56"/>
-      <c r="J523" s="56" t="s">
+      <c r="I523" s="55"/>
+      <c r="J523" s="55" t="s">
         <v>903</v>
       </c>
-      <c r="K523" s="58" t="s">
+      <c r="K523" s="57" t="s">
         <v>1433</v>
       </c>
     </row>
-    <row r="524" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A524" s="55">
+    <row r="524" spans="1:11" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A524" s="54">
         <v>3.8</v>
       </c>
-      <c r="B524" s="56" t="s">
+      <c r="B524" s="55" t="s">
         <v>170</v>
       </c>
-      <c r="C524" s="56" t="s">
+      <c r="C524" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="D524" s="56" t="s">
+      <c r="D524" s="55" t="s">
         <v>1429</v>
       </c>
-      <c r="E524" s="57"/>
-      <c r="F524" s="57"/>
-      <c r="G524" s="56"/>
-      <c r="H524" s="56" t="s">
+      <c r="E524" s="56"/>
+      <c r="F524" s="56"/>
+      <c r="G524" s="55"/>
+      <c r="H524" s="55" t="s">
         <v>641</v>
       </c>
-      <c r="I524" s="56"/>
-      <c r="J524" s="56" t="s">
+      <c r="I524" s="55"/>
+      <c r="J524" s="55" t="s">
         <v>903</v>
       </c>
-      <c r="K524" s="58" t="s">
+      <c r="K524" s="57" t="s">
         <v>1432</v>
       </c>
     </row>
-    <row r="525" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A525" s="55">
+    <row r="525" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A525" s="54">
         <v>3.8</v>
       </c>
-      <c r="B525" s="56" t="s">
+      <c r="B525" s="55" t="s">
         <v>170</v>
       </c>
-      <c r="C525" s="56" t="s">
+      <c r="C525" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="D525" s="56" t="s">
+      <c r="D525" s="55" t="s">
         <v>147</v>
       </c>
-      <c r="E525" s="57"/>
-      <c r="F525" s="57" t="s">
+      <c r="E525" s="56"/>
+      <c r="F525" s="56" t="s">
         <v>1441</v>
       </c>
-      <c r="G525" s="56"/>
-      <c r="H525" s="56" t="s">
+      <c r="G525" s="55"/>
+      <c r="H525" s="55" t="s">
         <v>1435</v>
       </c>
-      <c r="I525" s="56" t="s">
+      <c r="I525" s="55" t="s">
         <v>1439</v>
       </c>
-      <c r="J525" s="56" t="s">
+      <c r="J525" s="55" t="s">
         <v>903</v>
       </c>
-      <c r="K525" s="58" t="s">
+      <c r="K525" s="57" t="s">
         <v>1434</v>
       </c>
     </row>
-    <row r="526" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A526" s="55">
+    <row r="526" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A526" s="54">
         <v>3.8</v>
       </c>
-      <c r="B526" s="56" t="s">
+      <c r="B526" s="55" t="s">
         <v>531</v>
       </c>
-      <c r="C526" s="56" t="s">
+      <c r="C526" s="55" t="s">
         <v>173</v>
       </c>
-      <c r="D526" s="56" t="s">
+      <c r="D526" s="55" t="s">
         <v>1436</v>
       </c>
-      <c r="E526" s="57"/>
-      <c r="F526" s="57"/>
-      <c r="G526" s="56"/>
-      <c r="H526" s="56" t="s">
+      <c r="E526" s="56"/>
+      <c r="F526" s="56"/>
+      <c r="G526" s="55"/>
+      <c r="H526" s="55" t="s">
         <v>609</v>
       </c>
-      <c r="I526" s="56" t="s">
+      <c r="I526" s="55" t="s">
         <v>1438</v>
       </c>
-      <c r="J526" s="56" t="s">
+      <c r="J526" s="55" t="s">
         <v>531</v>
       </c>
-      <c r="K526" s="58" t="s">
+      <c r="K526" s="57" t="s">
         <v>1437</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K526" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:K526" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Agua 51"/>
+        <filter val="Agua Sledge"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L526">
     <sortCondition ref="A2:A526"/>
     <sortCondition ref="B2:B526"/>
